--- a/ET/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -90,6 +90,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF6B5B44"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>CollisionRadius</t>
     </r>
     <r>
@@ -1375,7 +1382,7 @@
         <v>1001</v>
       </c>
       <c r="L6" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M6" s="9"/>
     </row>

--- a/ET/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t>cs</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>碰撞半径</t>
+  </si>
+  <si>
+    <t>普攻</t>
+  </si>
+  <si>
+    <t>高度</t>
   </si>
   <si>
     <t>Id</t>
@@ -110,6 +116,12 @@
     </r>
   </si>
   <si>
+    <t>BasicAttackSkillId</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -119,7 +131,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>初始英雄</t>
+    <t>女刀客</t>
   </si>
   <si>
     <t>标准初始英雄</t>
@@ -132,6 +144,9 @@
   </si>
   <si>
     <t>Assets/Res/Game/TeamGame/Spine/Hero/1/p0002_3.8_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>盾骑士</t>
   </si>
 </sst>
 </file>
@@ -144,7 +159,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +194,12 @@
       <sz val="10"/>
       <color rgb="FF5C4A32"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF5C4A32"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -689,137 +710,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -843,6 +864,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1194,8 +1218,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="C1:N7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -1208,10 +1232,10 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="12.125" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13">
+    <row r="1" spans="3:14">
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1223,7 +1247,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="3:13">
+    <row r="2" spans="3:14">
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1254,7 +1278,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="3:13">
+    <row r="3" ht="24" customHeight="1" spans="3:14">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1285,95 +1309,110 @@
       <c r="L3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" ht="15.75" spans="3:13">
+    <row r="4" ht="25.5" spans="3:14">
       <c r="C4" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" spans="3:13">
+    <row r="5" spans="3:14">
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="3:13">
+    <row r="6" ht="24" customHeight="1" spans="3:14">
       <c r="C6" s="8">
         <v>1001</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>24</v>
+      <c r="D6" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H6" s="8">
         <v>100</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J6" s="8">
         <v>1001</v>
@@ -1381,10 +1420,53 @@
       <c r="K6" s="8">
         <v>1001</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="10">
         <v>25</v>
       </c>
-      <c r="M6" s="9"/>
+      <c r="M6" s="10">
+        <v>100100</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="24" customHeight="1" spans="3:14">
+      <c r="C7" s="8">
+        <v>1003</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="8">
+        <v>100</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1001</v>
+      </c>
+      <c r="K7" s="8">
+        <v>100301</v>
+      </c>
+      <c r="L7" s="10">
+        <v>25</v>
+      </c>
+      <c r="M7" s="10">
+        <v>100300</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
